--- a/mock_backend_service/inputs/result.xlsx
+++ b/mock_backend_service/inputs/result.xlsx
@@ -343,22 +343,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="20.7109375" customWidth="1" style="1" min="1" max="1"/>
     <col width="70.7109375" customWidth="1" style="1" min="2" max="2"/>
     <col width="40.7109375" customWidth="1" style="1" min="3" max="3"/>
   </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -370,7 +362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -422,6 +414,11 @@
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Request</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -534,6 +531,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="409.6" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -619,6 +621,11 @@
 }
 }
 ```</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
         </is>
       </c>
     </row>
@@ -731,6 +738,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="409.6" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -820,6 +832,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="197.45" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -871,6 +888,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="220.5" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -922,6 +944,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="105.6" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -969,6 +996,11 @@
 "headers": {}
 }
 ```</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
         </is>
       </c>
     </row>
@@ -1022,6 +1054,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="209.1" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
@@ -1073,6 +1110,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="197.45" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
@@ -1122,6 +1164,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="162.95" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
@@ -1172,6 +1219,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="162.95" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
@@ -1221,6 +1273,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="162.95" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
@@ -1268,6 +1325,11 @@
 "headers": {}
 }
 ```</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
         </is>
       </c>
     </row>
@@ -1323,6 +1385,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="300.95" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
@@ -1376,6 +1443,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="220.5" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
@@ -1428,6 +1500,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="220.5" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
@@ -1479,6 +1556,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="220.5" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
@@ -1528,6 +1610,11 @@
 }
 }
 ```</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
         </is>
       </c>
     </row>
@@ -1585,6 +1672,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="174.6" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
@@ -1633,6 +1725,11 @@
 "headers": {}
 }
 ```</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
         </is>
       </c>
     </row>
@@ -1712,6 +1809,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="381.95" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -1777,6 +1879,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="174.6" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
@@ -1827,6 +1934,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="174.6" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
@@ -1876,6 +1988,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="174.6" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
@@ -1925,6 +2042,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="186" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
@@ -1975,6 +2097,11 @@
 ```</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="186" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
@@ -2022,6 +2149,11 @@
 "headers": {}
 }
 ```</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Data Insufficient</t>
         </is>
       </c>
     </row>

--- a/mock_backend_service/inputs/result.xlsx
+++ b/mock_backend_service/inputs/result.xlsx
@@ -362,7 +362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -419,6 +419,11 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -536,6 +541,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="409.6" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -626,6 +636,11 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>Data Insufficient</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
         </is>
       </c>
     </row>
@@ -743,6 +758,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="409.6" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -837,6 +857,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="197.45" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -893,6 +918,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="220.5" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -949,6 +979,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="105.6" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -1001,6 +1036,11 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>Data Insufficient</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
         </is>
       </c>
     </row>
@@ -1059,6 +1099,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="209.1" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
@@ -1115,6 +1160,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="197.45" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
@@ -1169,6 +1219,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="162.95" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
@@ -1224,6 +1279,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="162.95" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
@@ -1278,6 +1338,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="162.95" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
@@ -1330,6 +1395,11 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>Data Insufficient</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
         </is>
       </c>
     </row>
@@ -1390,6 +1460,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="300.95" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
@@ -1448,6 +1523,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="220.5" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
@@ -1505,6 +1585,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="220.5" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
@@ -1561,6 +1646,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="220.5" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
@@ -1615,6 +1705,11 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>Data Insufficient</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
         </is>
       </c>
     </row>
@@ -1677,6 +1772,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="174.6" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
@@ -1730,6 +1830,11 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>Data Insufficient</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
         </is>
       </c>
     </row>
@@ -1814,6 +1919,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="381.95" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -1884,6 +1994,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="174.6" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
@@ -1939,6 +2054,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="174.6" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
@@ -1993,6 +2113,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="174.6" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
@@ -2047,6 +2172,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="186" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
@@ -2102,6 +2232,11 @@
           <t>Data Insufficient</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="186" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
@@ -2154,6 +2289,11 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>Data Insufficient</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Missing operationId and method</t>
         </is>
       </c>
     </row>

--- a/mock_backend_service/inputs/result.xlsx
+++ b/mock_backend_service/inputs/result.xlsx
@@ -427,7 +427,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="409.6" customHeight="1">
+    <row r="2" ht="396.75" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>AddPet_001: Add a new pet with valid data</t>
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>```json
+          <t xml:space="preserve">
 {
 "method": "POST",
 "url": "https://petstore.swagger.io/v2/pet",
@@ -532,8 +532,7 @@
 ],
 "status": "available"
 }
-}
-```</t>
+}</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
